--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_magallanes_y_la_antartica_chilena.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Total_Regional" sheetId="1" r:id="rId1"/>
     <sheet name="Por_Sexo" sheetId="2" r:id="rId2"/>
-    <sheet name="Por_Edad" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Prov" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Edad" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -364,19 +365,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Cobertura</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria_lbl</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total
-Regional</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B2">
+        <v>184266</v>
+      </c>
+      <c r="C2">
+        <v>183235</v>
+      </c>
+      <c r="D2">
         <v>100.5626654296395</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -424,17 +450,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="C2">
-        <v>92796</v>
+        <v>91470</v>
       </c>
       <c r="D2">
-        <v>93226</v>
+        <v>90009</v>
       </c>
       <c r="E2">
-        <v>99.538755282861</v>
+        <v>101.623171016232</v>
       </c>
     </row>
     <row r="3">
@@ -445,17 +471,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="C3">
-        <v>91470</v>
+        <v>92796</v>
       </c>
       <c r="D3">
-        <v>90009</v>
+        <v>93226</v>
       </c>
       <c r="E3">
-        <v>101.623171016232</v>
+        <v>99.538755282861</v>
       </c>
     </row>
   </sheetData>
@@ -465,7 +491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -476,7 +502,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tramo_Edad</t>
+          <t>Provincia</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -503,17 +529,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0-14</t>
+          <t>Antártica Chilena</t>
         </is>
       </c>
       <c r="C2">
-        <v>67316</v>
+        <v>1993</v>
       </c>
       <c r="D2">
-        <v>74905</v>
+        <v>1968</v>
       </c>
       <c r="E2">
-        <v>89.86850010012682</v>
+        <v>101.270325203252</v>
       </c>
     </row>
     <row r="3">
@@ -524,17 +550,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15-29</t>
+          <t>Tierra del Fuego</t>
         </is>
       </c>
       <c r="C3">
-        <v>36259</v>
+        <v>8105</v>
       </c>
       <c r="D3">
-        <v>36739</v>
+        <v>8587</v>
       </c>
       <c r="E3">
-        <v>98.69348648575084</v>
+        <v>94.38686386398044</v>
       </c>
     </row>
     <row r="4">
@@ -545,17 +571,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30-44</t>
+          <t>Última Esperanza</t>
         </is>
       </c>
       <c r="C4">
-        <v>45234</v>
+        <v>29475</v>
       </c>
       <c r="D4">
-        <v>44580</v>
+        <v>25712</v>
       </c>
       <c r="E4">
-        <v>101.4670255720054</v>
+        <v>114.6351897946484</v>
       </c>
     </row>
     <row r="5">
@@ -566,17 +592,138 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45-64</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="C5">
-        <v>46005</v>
+        <v>144679</v>
       </c>
       <c r="D5">
-        <v>44668</v>
+        <v>146817</v>
       </c>
       <c r="E5">
-        <v>102.993194233008</v>
+        <v>98.54376536777076</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Desagregación 1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tramo_Edad</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>25184</v>
+      </c>
+      <c r="D2">
+        <v>28077</v>
+      </c>
+      <c r="E2">
+        <v>89.69619261317092</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>30641</v>
+      </c>
+      <c r="D3">
+        <v>35738</v>
+      </c>
+      <c r="E3">
+        <v>85.73787005428396</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10-14</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>11491</v>
+      </c>
+      <c r="D4">
+        <v>11090</v>
+      </c>
+      <c r="E4">
+        <v>103.6158701532913</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15-19</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>11564</v>
+      </c>
+      <c r="D5">
+        <v>11278</v>
+      </c>
+      <c r="E5">
+        <v>102.5359106224508</v>
       </c>
     </row>
     <row r="6">
@@ -587,17 +734,269 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>20-24</t>
         </is>
       </c>
       <c r="C6">
-        <v>28402</v>
+        <v>11038</v>
       </c>
       <c r="D6">
-        <v>26154</v>
+        <v>11270</v>
       </c>
       <c r="E6">
-        <v>108.5952435573908</v>
+        <v>97.94143744454303</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>13657</v>
+      </c>
+      <c r="D7">
+        <v>14191</v>
+      </c>
+      <c r="E7">
+        <v>96.23705165245579</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>15606</v>
+      </c>
+      <c r="D8">
+        <v>15897</v>
+      </c>
+      <c r="E8">
+        <v>98.16946593696923</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>15718</v>
+      </c>
+      <c r="D9">
+        <v>14965</v>
+      </c>
+      <c r="E9">
+        <v>105.0317407283662</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>13910</v>
+      </c>
+      <c r="D10">
+        <v>13718</v>
+      </c>
+      <c r="E10">
+        <v>101.3996209359965</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>12556</v>
+      </c>
+      <c r="D11">
+        <v>12544</v>
+      </c>
+      <c r="E11">
+        <v>100.0956632653061</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>11349</v>
+      </c>
+      <c r="D12">
+        <v>10823</v>
+      </c>
+      <c r="E12">
+        <v>104.8600203270812</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>55-59</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>10969</v>
+      </c>
+      <c r="D13">
+        <v>10708</v>
+      </c>
+      <c r="E13">
+        <v>102.4374299589092</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60-64</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>11131</v>
+      </c>
+      <c r="D14">
+        <v>10593</v>
+      </c>
+      <c r="E14">
+        <v>105.0788256395733</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>9937</v>
+      </c>
+      <c r="D15">
+        <v>9215</v>
+      </c>
+      <c r="E15">
+        <v>107.8350515463918</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70-74</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>6975</v>
+      </c>
+      <c r="D16">
+        <v>6837</v>
+      </c>
+      <c r="E16">
+        <v>102.0184291355858</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>75-79</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>4880</v>
+      </c>
+      <c r="D17">
+        <v>4404</v>
+      </c>
+      <c r="E17">
+        <v>110.8083560399637</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>80+</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>6610</v>
+      </c>
+      <c r="D18">
+        <v>5698</v>
+      </c>
+      <c r="E18">
+        <v>116.005616005616</v>
       </c>
     </row>
   </sheetData>
